--- a/B K Exports SOA.xlsx
+++ b/B K Exports SOA.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="73">
   <si>
     <t>invoice number</t>
   </si>
@@ -117,12 +117,6 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>need to give</t>
-  </si>
-  <si>
-    <t>need to take</t>
-  </si>
-  <si>
     <t>payment date</t>
   </si>
   <si>
@@ -165,9 +159,6 @@
     <t>dedcut</t>
   </si>
   <si>
-    <t>clear</t>
-  </si>
-  <si>
     <t>BK048</t>
   </si>
   <si>
@@ -202,6 +193,57 @@
   </si>
   <si>
     <t>discount</t>
+  </si>
+  <si>
+    <t>26-27</t>
+  </si>
+  <si>
+    <t>Invoice number</t>
+  </si>
+  <si>
+    <t>total payment</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>BK002</t>
+  </si>
+  <si>
+    <t>BK003</t>
+  </si>
+  <si>
+    <t>BK004</t>
+  </si>
+  <si>
+    <t>BK005</t>
+  </si>
+  <si>
+    <t>BK011</t>
+  </si>
+  <si>
+    <t>BK012</t>
+  </si>
+  <si>
+    <t>BK013</t>
+  </si>
+  <si>
+    <t>BK015</t>
+  </si>
+  <si>
+    <t>BK016</t>
+  </si>
+  <si>
+    <t>BK017</t>
+  </si>
+  <si>
+    <t>BK018</t>
+  </si>
+  <si>
+    <t>BK019</t>
+  </si>
+  <si>
+    <t>BK020</t>
   </si>
 </sst>
 </file>
@@ -323,32 +365,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -367,99 +397,97 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -469,12 +497,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -493,25 +515,12 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -539,32 +548,9 @@
     <xf numFmtId="4" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -574,9 +560,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -591,6 +574,90 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -906,15 +973,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="11"/>
+    <col min="3" max="3" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="8"/>
     <col min="7" max="7" width="23.7109375" customWidth="1"/>
     <col min="13" max="13" width="28.7109375" customWidth="1"/>
     <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -927,16 +994,16 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
       <c r="G1" t="s">
@@ -950,25 +1017,25 @@
       <c r="B2" s="3">
         <v>7919.25</v>
       </c>
-      <c r="C2" s="66">
+      <c r="C2" s="56">
         <v>17843</v>
       </c>
-      <c r="D2" s="75">
+      <c r="D2" s="79">
         <v>17843</v>
       </c>
-      <c r="E2" s="72">
+      <c r="E2" s="91">
         <v>45810</v>
       </c>
-      <c r="F2" s="63">
+      <c r="F2" s="53">
         <f>C2-D2</f>
         <v>0</v>
       </c>
-      <c r="K2" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
+      <c r="K2" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -977,19 +1044,19 @@
       <c r="B3" s="3">
         <v>9923.2900000000009</v>
       </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="65"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="55"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -999,30 +1066,30 @@
       <c r="B4" s="3">
         <v>9118.02</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="11">
         <f>B4</f>
         <v>9118.02</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="81">
         <v>9118.02</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="92">
         <v>45814</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="29">
         <f>C4-D4</f>
         <v>0</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="59">
+      <c r="L4" s="51">
         <v>17843</v>
       </c>
-      <c r="M4" s="57">
+      <c r="M4" s="49">
         <v>17843</v>
       </c>
-      <c r="N4" s="58">
+      <c r="N4" s="50">
         <v>45810</v>
       </c>
     </row>
@@ -1033,25 +1100,25 @@
       <c r="B5" s="3">
         <v>10472.85</v>
       </c>
-      <c r="C5" s="68">
+      <c r="C5" s="58">
         <v>19109.25</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="82">
         <v>19109.25</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="93">
         <v>45827</v>
       </c>
-      <c r="F5" s="70">
+      <c r="F5" s="59">
         <f>C5-D5</f>
         <v>0</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="59"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="59"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="51"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1060,20 +1127,20 @@
       <c r="B6" s="3">
         <v>8636.4</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="71"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="60"/>
       <c r="K6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="7">
         <v>9118</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="7">
         <v>9118</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N6" s="6">
         <v>45814</v>
       </c>
     </row>
@@ -1084,33 +1151,31 @@
       <c r="B7" s="3">
         <v>9999.76</v>
       </c>
-      <c r="C7" s="66">
+      <c r="C7" s="56">
         <f>B7+B8+B9</f>
         <v>25190.3</v>
       </c>
-      <c r="D7" s="75">
+      <c r="D7" s="79">
         <v>5632.5</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="93">
         <v>45866</v>
       </c>
-      <c r="F7" s="82">
+      <c r="F7" s="65">
         <f>C7-D7-D9</f>
         <v>-1043.6599999999999</v>
       </c>
-      <c r="G7" s="54" t="s">
-        <v>30</v>
-      </c>
+      <c r="G7" s="48"/>
       <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="60">
+      <c r="L7" s="52">
         <v>19109</v>
       </c>
-      <c r="M7" s="59">
+      <c r="M7" s="51">
         <v>19109</v>
       </c>
-      <c r="N7" s="58">
+      <c r="N7" s="50">
         <v>45827</v>
       </c>
     </row>
@@ -1121,17 +1186,17 @@
       <c r="B8" s="3">
         <v>8615.16</v>
       </c>
-      <c r="C8" s="88"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="87"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="54"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="48"/>
       <c r="K8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="60"/>
-      <c r="M8" s="59"/>
-      <c r="N8" s="58"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="50"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -1140,23 +1205,23 @@
       <c r="B9" s="3">
         <v>6575.38</v>
       </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="20">
+      <c r="C9" s="57"/>
+      <c r="D9" s="81">
         <v>20601.46</v>
       </c>
-      <c r="E9" s="62"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="48"/>
       <c r="K9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="59">
+      <c r="L9" s="51">
         <v>25190</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="7">
         <v>5632</v>
       </c>
-      <c r="N9" s="58">
+      <c r="N9" s="50">
         <v>45866</v>
       </c>
     </row>
@@ -1167,31 +1232,29 @@
       <c r="B10" s="3">
         <v>7827.3</v>
       </c>
-      <c r="C10" s="85">
+      <c r="C10" s="68">
         <f>B10+B11</f>
         <v>17788.939999999999</v>
       </c>
-      <c r="D10" s="89">
+      <c r="D10" s="83">
         <v>16954.599999999999</v>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="93">
         <v>45870</v>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="53">
         <f>C10-D10</f>
         <v>834.34000000000015</v>
       </c>
-      <c r="G10" s="54" t="s">
-        <v>31</v>
-      </c>
+      <c r="G10" s="48"/>
       <c r="K10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="59"/>
-      <c r="M10" s="59">
+      <c r="L10" s="51"/>
+      <c r="M10" s="51">
         <v>20601</v>
       </c>
-      <c r="N10" s="59"/>
+      <c r="N10" s="51"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
@@ -1200,17 +1263,17 @@
       <c r="B11" s="3">
         <v>9961.64</v>
       </c>
-      <c r="C11" s="86"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="54"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="48"/>
       <c r="K11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L11" s="59"/>
-      <c r="M11" s="59"/>
-      <c r="N11" s="59"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -1219,34 +1282,32 @@
       <c r="B12" s="3">
         <v>10487.4</v>
       </c>
-      <c r="C12" s="85">
+      <c r="C12" s="68">
         <f>B12+B13</f>
         <v>20081.010000000002</v>
       </c>
-      <c r="D12" s="75">
+      <c r="D12" s="79">
         <v>19870</v>
       </c>
-      <c r="E12" s="61">
+      <c r="E12" s="93">
         <v>45874</v>
       </c>
-      <c r="F12" s="63">
+      <c r="F12" s="53">
         <f>C12-D12</f>
         <v>211.01000000000204</v>
       </c>
-      <c r="G12" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="6"/>
+      <c r="G12" s="48"/>
+      <c r="I12" s="5"/>
       <c r="K12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L12" s="59">
+      <c r="L12" s="51">
         <v>17789</v>
       </c>
-      <c r="M12" s="60">
+      <c r="M12" s="52">
         <v>16954</v>
       </c>
-      <c r="N12" s="58">
+      <c r="N12" s="50">
         <v>45870</v>
       </c>
     </row>
@@ -1257,17 +1318,17 @@
       <c r="B13" s="3">
         <v>9593.61</v>
       </c>
-      <c r="C13" s="86"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="54"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="48"/>
       <c r="K13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L13" s="59"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="59"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="51"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1276,33 +1337,31 @@
       <c r="B14" s="3">
         <v>10343.030000000001</v>
       </c>
-      <c r="C14" s="85">
+      <c r="C14" s="68">
         <f>B14+B15</f>
         <v>21994.18</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="79">
         <v>22506.639999999999</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="93">
         <v>45897</v>
       </c>
-      <c r="F14" s="63">
+      <c r="F14" s="53">
         <f>C14-D14</f>
         <v>-512.45999999999913</v>
       </c>
-      <c r="G14" s="54" t="s">
-        <v>30</v>
-      </c>
+      <c r="G14" s="48"/>
       <c r="K14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L14" s="59">
+      <c r="L14" s="51">
         <v>20081</v>
       </c>
-      <c r="M14" s="59">
+      <c r="M14" s="51">
         <v>19870</v>
       </c>
-      <c r="N14" s="58">
+      <c r="N14" s="50">
         <v>45874</v>
       </c>
     </row>
@@ -1313,17 +1372,17 @@
       <c r="B15" s="3">
         <v>11651.15</v>
       </c>
-      <c r="C15" s="86"/>
-      <c r="D15" s="76"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="54"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="48"/>
       <c r="K15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L15" s="59"/>
-      <c r="M15" s="59"/>
-      <c r="N15" s="59"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="51"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -1332,33 +1391,31 @@
       <c r="B16" s="3">
         <v>9620.1299999999992</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="11">
         <f>B16</f>
         <v>9620.1299999999992</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="81">
         <v>10448.1</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="92">
         <v>45930</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="29">
         <f>C16-D16</f>
         <v>-827.97000000000116</v>
       </c>
-      <c r="G16" s="14" t="s">
-        <v>30</v>
-      </c>
+      <c r="G16" s="10"/>
       <c r="K16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="13">
         <v>21994</v>
       </c>
-      <c r="M16" s="17">
+      <c r="M16" s="13">
         <v>22506</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="14">
         <v>45897</v>
       </c>
     </row>
@@ -1369,23 +1426,21 @@
       <c r="B17" s="4">
         <v>8801.9</v>
       </c>
-      <c r="C17" s="98">
+      <c r="C17" s="72">
         <f>B17+B18</f>
         <v>18510.77</v>
       </c>
-      <c r="D17" s="100">
+      <c r="D17" s="73">
         <v>15018</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E17" s="96">
         <v>45946</v>
       </c>
-      <c r="F17" s="98">
+      <c r="F17" s="72">
         <f>C17-D17</f>
         <v>3492.7700000000004</v>
       </c>
-      <c r="G17" s="97" t="s">
-        <v>31</v>
-      </c>
+      <c r="G17" s="71"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -1394,13 +1449,13 @@
       <c r="B18" s="4">
         <v>9708.8700000000008</v>
       </c>
-      <c r="C18" s="99"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="97"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="71"/>
       <c r="M18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N18">
         <v>3492</v>
@@ -1413,23 +1468,21 @@
       <c r="B19" s="4">
         <v>9192.35</v>
       </c>
-      <c r="C19" s="98">
+      <c r="C19" s="72">
         <f>B19+B20+B21+B22</f>
         <v>32852.65</v>
       </c>
-      <c r="D19" s="77">
+      <c r="D19" s="84">
         <v>20179.62</v>
       </c>
-      <c r="E19" s="78">
+      <c r="E19" s="97">
         <v>45959</v>
       </c>
-      <c r="F19" s="79">
+      <c r="F19" s="62">
         <f>C19-D19-D21</f>
         <v>3503.0300000000025</v>
       </c>
-      <c r="G19" s="97" t="s">
-        <v>31</v>
-      </c>
+      <c r="G19" s="71"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -1438,13 +1491,13 @@
       <c r="B20" s="4">
         <v>5823.61</v>
       </c>
-      <c r="C20" s="99"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="97"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="71"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -1453,15 +1506,15 @@
       <c r="B21" s="4">
         <v>8138.34</v>
       </c>
-      <c r="C21" s="99"/>
-      <c r="D21" s="19">
+      <c r="C21" s="73"/>
+      <c r="D21" s="8">
         <v>9170</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="98">
         <v>45960</v>
       </c>
-      <c r="F21" s="80"/>
-      <c r="G21" s="97"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="71"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -1470,9 +1523,9 @@
       <c r="B22" s="4">
         <v>9698.35</v>
       </c>
-      <c r="C22" s="99"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="97"/>
+      <c r="C22" s="73"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="71"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -1481,23 +1534,21 @@
       <c r="B23" s="4">
         <v>8123.74</v>
       </c>
-      <c r="C23" s="79">
+      <c r="C23" s="62">
         <f>B23+B24</f>
         <v>18721.400000000001</v>
       </c>
-      <c r="D23" s="91">
+      <c r="D23" s="85">
         <v>22291.21</v>
       </c>
-      <c r="E23" s="93">
+      <c r="E23" s="99">
         <v>45981</v>
       </c>
-      <c r="F23" s="95">
+      <c r="F23" s="62">
         <f>C23-D23</f>
         <v>-3569.8099999999977</v>
       </c>
-      <c r="G23" s="97" t="s">
-        <v>30</v>
-      </c>
+      <c r="G23" s="71"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -1506,87 +1557,83 @@
       <c r="B24" s="4">
         <v>10597.66</v>
       </c>
-      <c r="C24" s="81"/>
-      <c r="D24" s="92"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="97"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="71"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B25" s="4">
         <v>8084.34</v>
       </c>
-      <c r="C25" s="48">
+      <c r="C25" s="45">
         <f>B25+B26</f>
         <v>17122.580000000002</v>
       </c>
-      <c r="D25" s="50">
+      <c r="D25" s="38">
         <v>20031.18</v>
       </c>
-      <c r="E25" s="47">
+      <c r="E25" s="100">
         <v>46029</v>
       </c>
-      <c r="F25" s="39">
+      <c r="F25" s="45">
         <f>C25-D25</f>
         <v>-2908.5999999999985</v>
       </c>
-      <c r="G25" s="54" t="s">
-        <v>30</v>
-      </c>
+      <c r="G25" s="48"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B26" s="4">
         <v>9038.24</v>
       </c>
-      <c r="C26" s="53"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="54"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="48"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B27" s="4">
         <v>8311.7099999999991</v>
       </c>
-      <c r="C27" s="48">
+      <c r="C27" s="45">
         <f>B27+B28</f>
         <v>16174.68</v>
       </c>
-      <c r="D27" s="50">
+      <c r="D27" s="38">
         <v>15028</v>
       </c>
-      <c r="E27" s="56">
+      <c r="E27" s="101">
         <v>46039</v>
       </c>
-      <c r="F27" s="39">
+      <c r="F27" s="45">
         <f>C27-D27</f>
         <v>1146.6800000000003</v>
       </c>
-      <c r="G27" s="52" t="s">
-        <v>31</v>
-      </c>
+      <c r="G27" s="46"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B28" s="4">
         <v>7862.97</v>
       </c>
-      <c r="C28" s="49"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="52"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="46"/>
       <c r="L28">
         <v>39</v>
       </c>
@@ -1599,25 +1646,25 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29" s="4">
         <v>10574.88</v>
       </c>
-      <c r="C29" s="48">
+      <c r="C29" s="45">
         <v>20400</v>
       </c>
-      <c r="D29" s="50">
+      <c r="D29" s="38">
         <v>20400</v>
       </c>
-      <c r="E29" s="56">
+      <c r="E29" s="101">
         <v>46051</v>
       </c>
-      <c r="F29" s="39">
+      <c r="F29" s="45">
         <f>C29-D29</f>
         <v>0</v>
       </c>
-      <c r="G29" s="54"/>
+      <c r="G29" s="48"/>
       <c r="L29">
         <v>40</v>
       </c>
@@ -1630,16 +1677,16 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B30" s="4">
         <v>9825.43</v>
       </c>
-      <c r="C30" s="49"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="54"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="48"/>
       <c r="L30">
         <v>46</v>
       </c>
@@ -1653,28 +1700,26 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1">
         <v>9877.56</v>
       </c>
-      <c r="C31" s="48">
+      <c r="C31" s="45">
         <f>B31+B32-600</f>
         <v>19435.419999999998</v>
       </c>
-      <c r="D31" s="50">
+      <c r="D31" s="38">
         <v>19000</v>
       </c>
-      <c r="E31" s="56">
+      <c r="E31" s="101">
         <v>46092</v>
       </c>
-      <c r="F31" s="39">
+      <c r="F31" s="45">
         <f>C31-D31</f>
         <v>435.41999999999825</v>
       </c>
-      <c r="G31" s="54" t="s">
-        <v>46</v>
-      </c>
+      <c r="G31" s="48"/>
       <c r="M31">
         <f>SUM(M28:M30)</f>
         <v>20487.07</v>
@@ -1682,136 +1727,397 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B32" s="4">
         <v>10157.86</v>
       </c>
-      <c r="C32" s="49"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="54"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="48"/>
       <c r="L32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M32">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="4"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="26"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="4">
+        <v>10700</v>
+      </c>
+      <c r="C33" s="16">
+        <v>10700</v>
+      </c>
+      <c r="D33" s="87">
+        <v>10700</v>
+      </c>
+      <c r="E33" s="102">
+        <v>46127</v>
+      </c>
+      <c r="F33" s="28">
+        <f>C33-D33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" s="4">
-        <v>10700</v>
-      </c>
-      <c r="C34" s="22">
-        <v>10700</v>
-      </c>
-      <c r="D34" s="27">
-        <v>10700</v>
-      </c>
-      <c r="E34" s="28">
-        <v>46127</v>
-      </c>
-      <c r="F34" s="22">
+        <v>45</v>
+      </c>
+      <c r="B34" s="15">
+        <v>10258.86</v>
+      </c>
+      <c r="C34" s="44">
+        <f>B34+B35</f>
+        <v>20099.34</v>
+      </c>
+      <c r="D34" s="88">
+        <v>18000</v>
+      </c>
+      <c r="E34" s="103">
+        <v>46137</v>
+      </c>
+      <c r="F34" s="106">
         <f>C34-D34</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2099.34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="21">
-        <v>10258.86</v>
-      </c>
-      <c r="C35" s="41">
-        <f>B35+B36</f>
-        <v>20099.34</v>
-      </c>
-      <c r="D35" s="44">
-        <v>18000</v>
-      </c>
-      <c r="E35" s="42">
-        <v>46137</v>
-      </c>
-      <c r="F35" s="41">
-        <f>C35-D35</f>
-        <v>2099.34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="4">
+        <v>9840.48</v>
+      </c>
+      <c r="C35" s="43"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="39"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="4">
+        <v>46</v>
+      </c>
+      <c r="B36" s="15">
+        <v>10385.280000000001</v>
+      </c>
+      <c r="C36" s="40">
+        <f>B36+B37</f>
+        <v>20145.5</v>
+      </c>
+      <c r="D36" s="38">
+        <v>22100</v>
+      </c>
+      <c r="E36" s="100">
+        <v>46155</v>
+      </c>
+      <c r="F36" s="45">
+        <f>C36-D36</f>
+        <v>-1954.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="15">
+        <v>9760.2199999999993</v>
+      </c>
+      <c r="C37" s="43"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="4">
         <v>9840.48</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="40"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="21">
-        <v>10385.280000000001</v>
-      </c>
-      <c r="C37" s="39">
-        <f>B37+B38</f>
-        <v>20145.5</v>
-      </c>
-      <c r="D37" s="46">
-        <v>22100</v>
-      </c>
-      <c r="E37" s="47">
-        <v>46155</v>
-      </c>
-      <c r="F37" s="39">
-        <f>C37-D37</f>
-        <v>-1954.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38" s="21">
-        <v>9760.2199999999993</v>
-      </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C39" s="13">
-        <f>SUM(C2:C38)</f>
-        <v>334907.17</v>
-      </c>
-      <c r="D39" s="29">
-        <f>SUM(D2:D38)</f>
-        <v>334001.58</v>
-      </c>
-      <c r="F39" s="13">
+      <c r="C38" s="9">
+        <f>B38</f>
+        <v>9840.48</v>
+      </c>
+      <c r="D38" s="90">
+        <v>9840.48</v>
+      </c>
+      <c r="E38" s="98">
+        <v>46156</v>
+      </c>
+      <c r="F38" s="9">
+        <f>C38-D38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="32">
         <f>SUM(F2:F38)</f>
         <v>905.59000000000742</v>
       </c>
     </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="37"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="34">
+        <v>10147.14</v>
+      </c>
+      <c r="C44" s="27">
+        <f>B44</f>
+        <v>10147.14</v>
+      </c>
+      <c r="D44" s="35">
+        <v>10147.14</v>
+      </c>
+      <c r="E44" s="105">
+        <v>46171</v>
+      </c>
+      <c r="F44" s="30">
+        <f>C44-D44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="4">
+        <v>9402.43</v>
+      </c>
+      <c r="C45" s="9">
+        <f>B45</f>
+        <v>9402.43</v>
+      </c>
+      <c r="D45" s="9">
+        <f>C45</f>
+        <v>9402.43</v>
+      </c>
+      <c r="E45" s="98">
+        <v>46169</v>
+      </c>
+      <c r="F45" s="30">
+        <f>C45-D45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="4">
+        <v>9829.0499999999993</v>
+      </c>
+      <c r="C46" s="9">
+        <f>B46</f>
+        <v>9829.0499999999993</v>
+      </c>
+      <c r="D46" s="9">
+        <f>C46</f>
+        <v>9829.0499999999993</v>
+      </c>
+      <c r="E46" s="98">
+        <v>46255</v>
+      </c>
+      <c r="F46" s="30">
+        <f>C46-D46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="4">
+        <v>4619.3900000000003</v>
+      </c>
+      <c r="C47" s="9">
+        <f>B47</f>
+        <v>4619.3900000000003</v>
+      </c>
+      <c r="D47" s="9">
+        <f>C47</f>
+        <v>4619.3900000000003</v>
+      </c>
+      <c r="E47" s="98">
+        <v>46255</v>
+      </c>
+      <c r="F47" s="9">
+        <f>C47-D47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48" s="40">
+        <v>7933.63</v>
+      </c>
+      <c r="C48" s="42">
+        <f>B48</f>
+        <v>7933.63</v>
+      </c>
+      <c r="D48" s="36">
+        <v>5493.56</v>
+      </c>
+      <c r="E48" s="98">
+        <v>46255</v>
+      </c>
+      <c r="F48" s="45">
+        <f>C48-D48-D49</f>
+        <v>2420.12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="39"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="9">
+        <v>19.95</v>
+      </c>
+      <c r="E49" s="98">
+        <v>46253</v>
+      </c>
+      <c r="F49" s="39"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="4">
+        <v>8051.05</v>
+      </c>
+      <c r="C50" s="8">
+        <f>B50</f>
+        <v>8051.05</v>
+      </c>
+      <c r="D50" s="8">
+        <f>C50</f>
+        <v>8051.05</v>
+      </c>
+      <c r="E50" s="98">
+        <v>46254</v>
+      </c>
+      <c r="F50" s="8">
+        <f>C50-D50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="4">
+        <v>9474.08</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B52" s="4">
+        <v>7734.29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="4">
+        <v>9830.7000000000007</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" s="4">
+        <v>7897.75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="4">
+        <v>8144.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="4">
+        <v>5584.32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" s="4">
+        <v>9321.4</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="87">
+  <mergeCells count="92">
     <mergeCell ref="F29:F30"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G29:G30"/>
@@ -1891,14 +2197,19 @@
     <mergeCell ref="E25:E26"/>
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A41:F42"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="F48:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1925,151 +2236,153 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="32" t="s">
+      <c r="E1" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="99" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="101">
+      <c r="A2" s="73" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="74">
         <v>12400.07</v>
       </c>
-      <c r="C2" s="105">
+      <c r="C2" s="78">
         <f>B2</f>
         <v>12400.07</v>
       </c>
-      <c r="D2" s="33">
+      <c r="D2" s="20">
         <v>7721.09</v>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="21">
         <v>46127</v>
       </c>
-      <c r="F2" s="58"/>
-      <c r="G2" s="101">
+      <c r="F2" s="50"/>
+      <c r="G2" s="74">
         <f>C2-D2-D3</f>
         <v>-1090.2400000000007</v>
       </c>
-      <c r="H2" s="104"/>
-      <c r="I2" s="37"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="99"/>
-      <c r="B3" s="101"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="33">
+      <c r="A3" s="73"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="20">
         <v>5769.22</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="21">
         <v>46149</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="37"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B4" s="4">
         <v>11380.69</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="22">
         <v>11380.69</v>
       </c>
       <c r="D4" s="1">
         <v>6927.86</v>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="21">
         <v>46171</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="23">
         <v>100</v>
       </c>
       <c r="G4" s="4">
         <f>C4-D4-F4</f>
         <v>4352.8300000000008</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38">
+      <c r="H4" s="25"/>
+      <c r="I4" s="25">
         <f>G2+G4</f>
         <v>3262.59</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B5" s="4">
         <v>11290.33</v>
       </c>
-      <c r="C5" s="101">
+      <c r="C5" s="74">
         <f>B5+B6+B7</f>
         <v>30753.170000000002</v>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="49">
         <v>21861.38</v>
       </c>
-      <c r="E5" s="78">
+      <c r="E5" s="61">
         <v>46206</v>
       </c>
-      <c r="F5" s="103"/>
-      <c r="G5" s="102">
+      <c r="F5" s="76"/>
+      <c r="G5" s="75">
         <f>C5-D5-D7</f>
-        <v>8891.7900000000009</v>
-      </c>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
+        <v>1012.2300000000005</v>
+      </c>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B6" s="4">
         <v>8193.18</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B7" s="4">
         <v>11269.66</v>
       </c>
-      <c r="C7" s="59"/>
+      <c r="C7" s="51"/>
       <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="38">
+        <v>7879.56</v>
+      </c>
+      <c r="E7" s="26">
+        <v>46244</v>
+      </c>
+      <c r="F7" s="76"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="25">
         <f>G2+G4+G5</f>
-        <v>12154.380000000001</v>
+        <v>4274.8200000000006</v>
       </c>
     </row>
   </sheetData>
